--- a/data/performance/daily/signal_list_2026-06-25.xlsx
+++ b/data/performance/daily/signal_list_2026-06-25.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-25.xlsx
+++ b/data/performance/daily/signal_list_2026-06-25.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -563,12 +569,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -605,12 +616,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -642,17 +658,22 @@
       <c r="G7" s="4" t="n">
         <v>-1.31</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -689,12 +710,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -731,12 +757,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -773,12 +804,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -815,12 +851,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -852,17 +893,22 @@
       <c r="G12" s="4" t="n">
         <v>-3.42</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -879,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -889,9 +935,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -921,7 +968,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -946,15 +993,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -991,12 +1043,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1033,12 +1090,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1070,17 +1132,22 @@
       <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1117,12 +1184,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1159,12 +1231,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1196,17 +1273,22 @@
       <c r="G10" s="4" t="n">
         <v>-0.89</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1243,12 +1325,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1280,17 +1367,22 @@
       <c r="G12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1327,12 +1419,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1364,17 +1461,22 @@
       <c r="G14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1411,12 +1513,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1448,17 +1555,22 @@
       <c r="G16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1495,12 +1607,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1537,12 +1654,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1579,12 +1701,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1616,17 +1743,22 @@
       <c r="G20" s="4" t="n">
         <v>-7.28</v>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1663,12 +1795,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1705,12 +1842,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1747,12 +1889,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1784,17 +1931,22 @@
       <c r="G24" s="4" t="n">
         <v>-1.74</v>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1831,12 +1983,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1873,12 +2030,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1915,12 +2077,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1957,12 +2124,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1999,12 +2171,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2041,12 +2218,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2078,17 +2260,22 @@
       <c r="G31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2125,12 +2312,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2167,12 +2359,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2209,12 +2406,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2251,12 +2453,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2288,17 +2495,22 @@
       <c r="G36" s="4" t="n">
         <v>-3.42</v>
       </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-25.xlsx
+++ b/data/performance/daily/signal_list_2026-06-25.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>4013.87</v>
       </c>
       <c r="D5" t="n">
+        <v/>
+      </c>
+      <c r="E5" t="n">
         <v>4060</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>4070</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>16250</v>
       </c>
       <c r="D6" t="n">
+        <v/>
+      </c>
+      <c r="E6" t="n">
         <v>16900</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>17100</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>5.23</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>1145</v>
       </c>
       <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
         <v>1130</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>1160</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-1.31</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>1515</v>
       </c>
       <c r="D8" t="n">
-        <v>1520</v>
+        <v/>
       </c>
       <c r="E8" t="n">
         <v>1520</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>0.33</v>
+      <c r="F8" t="n">
+        <v>1520</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H8" s="4" t="n">
+        <v>0.33</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>955</v>
       </c>
       <c r="D9" t="n">
-        <v>980</v>
+        <v/>
       </c>
       <c r="E9" t="n">
         <v>980</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>2.62</v>
+      <c r="F9" t="n">
+        <v>980</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>2.62</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H9" s="4" t="n">
+        <v>2.62</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>374</v>
       </c>
       <c r="D10" t="n">
-        <v>384</v>
+        <v/>
       </c>
       <c r="E10" t="n">
         <v>384</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>2.67</v>
+      <c r="F10" t="n">
+        <v>384</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>2.67</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H10" s="4" t="n">
+        <v>2.67</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>173</v>
       </c>
       <c r="D11" t="n">
+        <v/>
+      </c>
+      <c r="E11" t="n">
         <v>202</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>216</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>24.86</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>16.76</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>585</v>
       </c>
       <c r="D12" t="n">
+        <v/>
+      </c>
+      <c r="E12" t="n">
         <v>565</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>590</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-3.42</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -925,7 +955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -933,12 +963,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -968,45 +999,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1027,33 +1063,36 @@
         <v>4770</v>
       </c>
       <c r="D5" t="n">
-        <v>4770</v>
+        <v/>
       </c>
       <c r="E5" t="n">
         <v>4770</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>0</v>
+      <c r="F5" t="n">
+        <v>4770</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1074,33 +1113,36 @@
         <v>4770</v>
       </c>
       <c r="D6" t="n">
-        <v>4770</v>
+        <v/>
       </c>
       <c r="E6" t="n">
         <v>4770</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>0</v>
+      <c r="F6" t="n">
+        <v>4770</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1121,33 +1163,36 @@
         <v>11800</v>
       </c>
       <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
         <v>11800</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>12150</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>2.97</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1168,33 +1213,36 @@
         <v>374</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v/>
       </c>
       <c r="E8" t="n">
         <v>378</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>1.07</v>
+      <c r="F8" t="n">
+        <v>378</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>1.07</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H8" s="4" t="n">
+        <v>1.07</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1215,33 +1263,36 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
         <v>70</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>78</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>14.71</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>2.94</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1262,33 +1313,36 @@
         <v>448</v>
       </c>
       <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
         <v>444</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>456</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>1.79</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-0.89</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1309,33 +1363,36 @@
         <v>2920</v>
       </c>
       <c r="D11" t="n">
-        <v>3160</v>
+        <v/>
       </c>
       <c r="E11" t="n">
         <v>3160</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>8.220000000000001</v>
+      <c r="F11" t="n">
+        <v>3160</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H11" s="4" t="n">
+        <v>8.220000000000001</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1356,33 +1413,36 @@
         <v>102</v>
       </c>
       <c r="D12" t="n">
+        <v/>
+      </c>
+      <c r="E12" t="n">
         <v>102</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>106</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>3.92</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1403,33 +1463,36 @@
         <v>492</v>
       </c>
       <c r="D13" t="n">
+        <v/>
+      </c>
+      <c r="E13" t="n">
         <v>496</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>510</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>3.66</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1450,33 +1513,36 @@
         <v>1860</v>
       </c>
       <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
         <v>1860</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>1870</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>0.54</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1497,33 +1563,36 @@
         <v>348</v>
       </c>
       <c r="D15" t="n">
-        <v>372</v>
+        <v/>
       </c>
       <c r="E15" t="n">
         <v>372</v>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>6.9</v>
+      <c r="F15" t="n">
+        <v>372</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H15" s="4" t="n">
+        <v>6.9</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1544,33 +1613,36 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
         <v>70</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>71</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>1.43</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1591,33 +1663,36 @@
         <v>650</v>
       </c>
       <c r="D17" t="n">
-        <v>675</v>
+        <v/>
       </c>
       <c r="E17" t="n">
         <v>675</v>
       </c>
-      <c r="F17" s="4" t="n">
-        <v>3.85</v>
+      <c r="F17" t="n">
+        <v>675</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>3.85</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H17" s="4" t="n">
+        <v>3.85</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1638,33 +1713,36 @@
         <v>710</v>
       </c>
       <c r="D18" t="n">
+        <v/>
+      </c>
+      <c r="E18" t="n">
         <v>720</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>840</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>18.31</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>1.41</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1685,33 +1763,36 @@
         <v>640</v>
       </c>
       <c r="D19" t="n">
-        <v>675</v>
+        <v/>
       </c>
       <c r="E19" t="n">
         <v>675</v>
       </c>
-      <c r="F19" s="4" t="n">
-        <v>5.47</v>
+      <c r="F19" t="n">
+        <v>675</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>5.47</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H19" s="4" t="n">
+        <v>5.47</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1732,33 +1813,36 @@
         <v>302</v>
       </c>
       <c r="D20" t="n">
+        <v/>
+      </c>
+      <c r="E20" t="n">
         <v>280</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>308</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>1.99</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>-7.28</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1779,33 +1863,36 @@
         <v>1845</v>
       </c>
       <c r="D21" t="n">
-        <v>1845</v>
+        <v/>
       </c>
       <c r="E21" t="n">
         <v>1845</v>
       </c>
-      <c r="F21" s="4" t="n">
-        <v>0</v>
+      <c r="F21" t="n">
+        <v>1845</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1826,33 +1913,36 @@
         <v>1490</v>
       </c>
       <c r="D22" t="n">
+        <v/>
+      </c>
+      <c r="E22" t="n">
         <v>1515</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>1660</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>11.41</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>1.68</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1873,33 +1963,36 @@
         <v>1185</v>
       </c>
       <c r="D23" t="n">
+        <v/>
+      </c>
+      <c r="E23" t="n">
         <v>1190</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>1205</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>1.69</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1920,33 +2013,36 @@
         <v>172</v>
       </c>
       <c r="D24" t="n">
+        <v/>
+      </c>
+      <c r="E24" t="n">
         <v>169</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>174</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>1.16</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>-1.74</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1967,33 +2063,36 @@
         <v>1405</v>
       </c>
       <c r="D25" t="n">
-        <v>1280</v>
+        <v/>
       </c>
       <c r="E25" t="n">
         <v>1280</v>
       </c>
-      <c r="F25" s="4" t="n">
-        <v>-8.9</v>
+      <c r="F25" t="n">
+        <v>1280</v>
       </c>
       <c r="G25" s="4" t="n">
         <v>-8.9</v>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H25" s="4" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="J25" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2014,33 +2113,36 @@
         <v>1530</v>
       </c>
       <c r="D26" t="n">
+        <v/>
+      </c>
+      <c r="E26" t="n">
         <v>1730</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>1850</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>20.92</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>13.07</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2061,33 +2163,36 @@
         <v>64</v>
       </c>
       <c r="D27" t="n">
+        <v/>
+      </c>
+      <c r="E27" t="n">
         <v>68</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>71</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>10.94</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>6.25</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2108,33 +2213,36 @@
         <v>4770</v>
       </c>
       <c r="D28" t="n">
-        <v>4770</v>
+        <v/>
       </c>
       <c r="E28" t="n">
         <v>4770</v>
       </c>
-      <c r="F28" s="4" t="n">
-        <v>0</v>
+      <c r="F28" t="n">
+        <v>4770</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="H28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="J28" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2155,33 +2263,36 @@
         <v>476</v>
       </c>
       <c r="D29" t="n">
+        <v/>
+      </c>
+      <c r="E29" t="n">
         <v>478</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>484</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>1.68</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2202,33 +2313,36 @@
         <v>374</v>
       </c>
       <c r="D30" t="n">
-        <v>384</v>
+        <v/>
       </c>
       <c r="E30" t="n">
         <v>384</v>
       </c>
-      <c r="F30" s="4" t="n">
-        <v>2.67</v>
+      <c r="F30" t="n">
+        <v>384</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>2.67</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H30" s="4" t="n">
+        <v>2.67</v>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2249,33 +2363,36 @@
         <v>65</v>
       </c>
       <c r="D31" t="n">
+        <v/>
+      </c>
+      <c r="E31" t="n">
         <v>65</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>68</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>4.62</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2296,33 +2413,36 @@
         <v>665</v>
       </c>
       <c r="D32" t="n">
+        <v/>
+      </c>
+      <c r="E32" t="n">
         <v>695</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>720</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>8.27</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>4.51</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2343,33 +2463,36 @@
         <v>136</v>
       </c>
       <c r="D33" t="n">
-        <v>141</v>
+        <v/>
       </c>
       <c r="E33" t="n">
         <v>141</v>
       </c>
-      <c r="F33" s="4" t="n">
-        <v>3.68</v>
+      <c r="F33" t="n">
+        <v>141</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>3.68</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H33" s="4" t="n">
+        <v>3.68</v>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2390,33 +2513,36 @@
         <v>600</v>
       </c>
       <c r="D34" t="n">
+        <v/>
+      </c>
+      <c r="E34" t="n">
         <v>595</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>600</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>-0.83</v>
       </c>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
+      <c r="J34" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2437,33 +2563,36 @@
         <v>1185</v>
       </c>
       <c r="D35" t="n">
+        <v/>
+      </c>
+      <c r="E35" t="n">
         <v>1250</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>1265</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>6.75</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>5.49</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2484,33 +2613,36 @@
         <v>585</v>
       </c>
       <c r="D36" t="n">
+        <v/>
+      </c>
+      <c r="E36" t="n">
         <v>565</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>590</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>-3.42</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-25.xlsx
+++ b/data/performance/daily/signal_list_2026-06-25.xlsx
@@ -559,7 +559,7 @@
         <v>4013.87</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>3980</v>
       </c>
       <c r="E5" t="n">
         <v>4060</v>
@@ -609,7 +609,7 @@
         <v>16250</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>15485</v>
       </c>
       <c r="E6" t="n">
         <v>16900</v>
@@ -659,7 +659,7 @@
         <v>1145</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>1145</v>
       </c>
       <c r="E7" t="n">
         <v>1130</v>
@@ -709,7 +709,7 @@
         <v>1515</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>1505.03</v>
       </c>
       <c r="E8" t="n">
         <v>1520</v>
@@ -759,7 +759,7 @@
         <v>955</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>955</v>
       </c>
       <c r="E9" t="n">
         <v>980</v>
@@ -809,7 +809,7 @@
         <v>374</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>374</v>
       </c>
       <c r="E10" t="n">
         <v>384</v>
@@ -859,7 +859,7 @@
         <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>176</v>
       </c>
       <c r="E11" t="n">
         <v>202</v>
@@ -909,7 +909,7 @@
         <v>585</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>585</v>
       </c>
       <c r="E12" t="n">
         <v>565</v>
@@ -1063,7 +1063,7 @@
         <v>4770</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>4760</v>
       </c>
       <c r="E5" t="n">
         <v>4770</v>
@@ -1113,7 +1113,7 @@
         <v>4770</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>4760</v>
       </c>
       <c r="E6" t="n">
         <v>4770</v>
@@ -1163,7 +1163,7 @@
         <v>11800</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>11800</v>
       </c>
       <c r="E7" t="n">
         <v>11800</v>
@@ -1213,7 +1213,7 @@
         <v>374</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>326.26</v>
       </c>
       <c r="E8" t="n">
         <v>378</v>
@@ -1263,7 +1263,7 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>70</v>
       </c>
       <c r="E9" t="n">
         <v>70</v>
@@ -1313,7 +1313,7 @@
         <v>448</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>448</v>
       </c>
       <c r="E10" t="n">
         <v>444</v>
@@ -1363,7 +1363,7 @@
         <v>2920</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>2930</v>
       </c>
       <c r="E11" t="n">
         <v>3160</v>
@@ -1413,7 +1413,7 @@
         <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
         <v>102</v>
@@ -1463,7 +1463,7 @@
         <v>492</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>498</v>
       </c>
       <c r="E13" t="n">
         <v>496</v>
@@ -1513,7 +1513,7 @@
         <v>1860</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>1614.33</v>
       </c>
       <c r="E14" t="n">
         <v>1860</v>
@@ -1563,7 +1563,7 @@
         <v>348</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>346</v>
       </c>
       <c r="E15" t="n">
         <v>372</v>
@@ -1613,7 +1613,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>69</v>
       </c>
       <c r="E16" t="n">
         <v>70</v>
@@ -1663,7 +1663,7 @@
         <v>650</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>606.3200000000001</v>
       </c>
       <c r="E17" t="n">
         <v>675</v>
@@ -1713,7 +1713,7 @@
         <v>710</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>710</v>
       </c>
       <c r="E18" t="n">
         <v>720</v>
@@ -1763,7 +1763,7 @@
         <v>640</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>640</v>
       </c>
       <c r="E19" t="n">
         <v>675</v>
@@ -1813,7 +1813,7 @@
         <v>302</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>273.85</v>
       </c>
       <c r="E20" t="n">
         <v>280</v>
@@ -1863,7 +1863,7 @@
         <v>1845</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>1845</v>
       </c>
       <c r="E21" t="n">
         <v>1845</v>
@@ -1913,7 +1913,7 @@
         <v>1490</v>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>1490</v>
       </c>
       <c r="E22" t="n">
         <v>1515</v>
@@ -1963,7 +1963,7 @@
         <v>1185</v>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>1180</v>
       </c>
       <c r="E23" t="n">
         <v>1190</v>
@@ -2013,7 +2013,7 @@
         <v>172</v>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>171</v>
       </c>
       <c r="E24" t="n">
         <v>169</v>
@@ -2063,7 +2063,7 @@
         <v>1405</v>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>1265</v>
       </c>
       <c r="E25" t="n">
         <v>1280</v>
@@ -2113,7 +2113,7 @@
         <v>1530</v>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>1525</v>
       </c>
       <c r="E26" t="n">
         <v>1730</v>
@@ -2163,7 +2163,7 @@
         <v>64</v>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>69</v>
       </c>
       <c r="E27" t="n">
         <v>68</v>
@@ -2213,7 +2213,7 @@
         <v>4770</v>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>4760</v>
       </c>
       <c r="E28" t="n">
         <v>4770</v>
@@ -2263,7 +2263,7 @@
         <v>476</v>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>476</v>
       </c>
       <c r="E29" t="n">
         <v>478</v>
@@ -2313,7 +2313,7 @@
         <v>374</v>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>374</v>
       </c>
       <c r="E30" t="n">
         <v>384</v>
@@ -2363,7 +2363,7 @@
         <v>65</v>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>65</v>
       </c>
       <c r="E31" t="n">
         <v>65</v>
@@ -2413,7 +2413,7 @@
         <v>665</v>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>665</v>
       </c>
       <c r="E32" t="n">
         <v>695</v>
@@ -2463,7 +2463,7 @@
         <v>136</v>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>135</v>
       </c>
       <c r="E33" t="n">
         <v>141</v>
@@ -2513,7 +2513,7 @@
         <v>600</v>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>600</v>
       </c>
       <c r="E34" t="n">
         <v>595</v>
@@ -2563,7 +2563,7 @@
         <v>1185</v>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>1179.94</v>
       </c>
       <c r="E35" t="n">
         <v>1250</v>
@@ -2613,7 +2613,7 @@
         <v>585</v>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>585</v>
       </c>
       <c r="E36" t="n">
         <v>565</v>
